--- a/outputs/per-fund/vc-investments-bain-capital-crypto.xlsx
+++ b/outputs/per-fund/vc-investments-bain-capital-crypto.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Bain Capital Crypto. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Bain Capital Crypto. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -7398,11 +7398,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, bain-capital-crypto</t>
+          <t>a16z-crypto, bain-capital-crypto, digital-currency-group</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -7524,11 +7524,11 @@
         <v>1</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, cmt-digital</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -7896,11 +7896,11 @@
         <v>1</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, dragonfly</t>
+          <t>bain-capital-crypto, dragonfly, hack-vc</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -8018,11 +8018,11 @@
         <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, cmt-digital</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -8081,11 +8081,11 @@
         <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm</t>
+          <t>bain-capital-crypto, hack-vc, paradigm</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -8144,11 +8144,11 @@
         <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, dragonfly, paradigm</t>
+          <t>bain-capital-crypto, dragonfly, hack-vc, paradigm</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -8270,11 +8270,11 @@
         <v>2</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, framework-ventures, pantera</t>
+          <t>bain-capital-crypto, coinbase-ventures, digital-currency-group, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -8396,11 +8396,11 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, digital-currency-group</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -8587,11 +8587,11 @@
         <v>2</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, delphi-ventures, figment-capital, maven11, polychain</t>
+          <t>bain-capital-crypto, blockchain-capital, coinbase-ventures, delphi-ventures, figment-capital, galaxy-digital, jump-crypto, maven11, mh-ventures, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -8650,11 +8650,11 @@
         <v>2</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm, robot-ventures</t>
+          <t>bain-capital-crypto, jump-crypto, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -8776,11 +8776,11 @@
         <v>1</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, delphi-ventures, figment-capital, maven11</t>
+          <t>bain-capital-crypto, blockchain-capital, delphi-ventures, fenbushi-capital, figment-capital, galaxy-digital, iosg-ventures, maven11</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -8839,11 +8839,11 @@
         <v>2</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, polychain, robot-ventures</t>
+          <t>bain-capital-crypto, hack-vc, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -8965,11 +8965,11 @@
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, galaxy-digital, gsr</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -9091,11 +9091,11 @@
         <v>2</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -9150,11 +9150,11 @@
         <v>1</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, robot-ventures</t>
+          <t>1kx, bain-capital-crypto, robot-ventures</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -9213,11 +9213,11 @@
         <v>2</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, dragonfly</t>
+          <t>bain-capital-crypto, coinbase-ventures, dragonfly, hack-vc</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -9276,11 +9276,11 @@
         <v>2</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, paradigm, robot-ventures</t>
+          <t>bain-capital-crypto, fenbushi-capital, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -9394,11 +9394,11 @@
         <v>0</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, bain-capital-crypto</t>
+          <t>a16z-crypto, bain-capital-crypto, mirana-ventures</t>
         </is>
       </c>
       <c r="M34" s="10" t="n"/>
@@ -9453,11 +9453,11 @@
         <v>1</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, galaxy-digital, sequoia-capital</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -9701,11 +9701,11 @@
         <v>2</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, haun-ventures</t>
+          <t>bain-capital-crypto, galaxy-digital, haun-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -9945,11 +9945,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto</t>
+          <t>bain-capital-crypto, circle-ventures, galaxy-digital, sequoia-capital</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -10008,11 +10008,11 @@
         <v>2</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, robot-ventures</t>
+          <t>bain-capital-crypto, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n">
@@ -11939,13 +11939,13 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Unieke uitgaande domeinen als benadering van portefeuillenamen.</t>
+          <t>Unique outbound domains as an approximation of portfolio names.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
